--- a/feedback_surveys/021_p2p_crypto_trading_feedback--feedback_surveys.xlsx
+++ b/feedback_surveys/021_p2p_crypto_trading_feedback--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1091,17 +1091,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>trade_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>p2p</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>P2P</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>p2p</t>
+          <t>escrow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>Escrow</t>
         </is>
       </c>
     </row>
@@ -1130,29 +1130,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>escrow</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Escrow</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trade_type_choices</t>
+          <t>security_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1181,29 +1181,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>security_choices</t>
+          <t>product_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>binance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Binance</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>binance</t>
+          <t>huobi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Huobi</t>
         </is>
       </c>
     </row>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>huobi</t>
+          <t>ftx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Huobi</t>
+          <t>FTX</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>community_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ftx</t>
+          <t>discord</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FTX</t>
+          <t>Discord</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>discord</t>
+          <t>telegram</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Telegram</t>
         </is>
       </c>
     </row>
@@ -1283,29 +1283,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>telegram</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Reddit</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>community_choices</t>
+          <t>platform_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Coinbase</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>coinbase</t>
+          <t>binance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Binance</t>
         </is>
       </c>
     </row>
@@ -1334,29 +1334,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>binance</t>
+          <t>kraken</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Kraken</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>platform_choices</t>
+          <t>trade_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kraken</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1385,29 +1385,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>trade_status_choices</t>
+          <t>trade_fees_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Percentage</t>
         </is>
       </c>
     </row>
@@ -1436,29 +1436,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Percentage</t>
+          <t>Variable</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trade_fees_type_choices</t>
+          <t>trade_fees_currency_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>variable</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1487,29 +1487,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>btc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>trade_fees_currency_choices</t>
+          <t>support_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>btc</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1538,27 +1538,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>live_chat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>support_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>live_chat</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Live Chat</t>
         </is>
